--- a/2.บัญชีรายชื่อสถานีแม่ข่าย 8 สถานที่.xlsx
+++ b/2.บัญชีรายชื่อสถานีแม่ข่าย 8 สถานที่.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chana\Desktop\report(PM)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BDF329-25E8-4A69-AAC0-5278333C9821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A28B97-BDBE-4CF3-9D37-D273FE59843C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BS!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BS!$A$1:$F$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BS!$A$1:$G$9</definedName>
     <definedName name="Z_061490AE_9771_4681_AB1E_117F960D9615_.wvu.FilterData" localSheetId="0" hidden="1">BS!#REF!</definedName>
     <definedName name="Z_597DB036_9A3B_4F97_98CA_81D367A37211_.wvu.FilterData" localSheetId="0" hidden="1">BS!#REF!</definedName>
     <definedName name="Z_63ECC3D9_4973_46D6_B790_673386230A18_.wvu.FilterData" localSheetId="0" hidden="1">BS!#REF!</definedName>
@@ -26,12 +26,12 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Np" guid="{502919B8-4F67-4683-8659-3862B70691FE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="JAY" guid="{597DB036-9A3B-4F97-98CA-81D367A37211}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="SHAME" guid="{061490AE-9771-4681-AB1E-117F960D9615}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filter Nu" guid="{A8F44D7B-F76C-4159-8A1E-48B65B53E2E6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filter 1" guid="{D215FCC6-D94B-4C3B-A67F-B7718DDCD7E5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="MEE" guid="{63ECC3D9-4973-46D6-B790-673386230A18}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filter 1" guid="{D215FCC6-D94B-4C3B-A67F-B7718DDCD7E5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filter Nu" guid="{A8F44D7B-F76C-4159-8A1E-48B65B53E2E6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="SHAME" guid="{061490AE-9771-4681-AB1E-117F960D9615}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="JAY" guid="{597DB036-9A3B-4F97-98CA-81D367A37211}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Np" guid="{502919B8-4F67-4683-8659-3862B70691FE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>อำเภอ</t>
   </si>
@@ -144,6 +144,33 @@
   <si>
     <t>Tower
 (m.)</t>
+  </si>
+  <si>
+    <t>สถานี</t>
+  </si>
+  <si>
+    <t>BS หนองนกแก้ว</t>
+  </si>
+  <si>
+    <t>BS ปางใหม่พัฒนา</t>
+  </si>
+  <si>
+    <t>BS ศรีสุขสำราญ</t>
+  </si>
+  <si>
+    <t>BS คลองพลู</t>
+  </si>
+  <si>
+    <t>BS ช่อง</t>
+  </si>
+  <si>
+    <t>BS คลองป่าหมู</t>
+  </si>
+  <si>
+    <t>BS วัดบางอุดม</t>
+  </si>
+  <si>
+    <t>BS วังงิ้ว</t>
   </si>
 </sst>
 </file>
@@ -331,11 +358,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -379,12 +408,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{4657CF72-648F-4367-A39B-A26ABBE1C716}"/>
+    <cellStyle name="Normal 2 3 2" xfId="3" xr:uid="{21AA8108-15F9-4425-B90C-F9024676AC59}"/>
+    <cellStyle name="Normal 2 4" xfId="2" xr:uid="{BF613F9E-676D-4669-B6A2-1D1E63EEB2E2}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -595,236 +640,265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E19205-E86C-41CF-A151-E7AA497D2CE5}">
-  <dimension ref="A1:G792"/>
+  <dimension ref="A1:H792"/>
   <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.69921875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.296875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.69921875" style="1"/>
+    <col min="2" max="2" width="19.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.69921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.296875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>14.514783</v>
       </c>
-      <c r="F2" s="5">
+      <c r="G2" s="5">
         <v>99.709058999999996</v>
       </c>
-      <c r="G2" s="12">
+      <c r="H2" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>15.993741</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G3" s="5">
         <v>99.364570999999998</v>
       </c>
-      <c r="G3" s="12">
+      <c r="H3" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>16.919523999999999</v>
       </c>
-      <c r="F4" s="5">
+      <c r="G4" s="5">
         <v>102.72752300000001</v>
       </c>
-      <c r="G4" s="12">
+      <c r="H4" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>12.935093999999999</v>
       </c>
-      <c r="F5" s="7">
+      <c r="G5" s="7">
         <v>102.05857399999999</v>
       </c>
-      <c r="G5" s="12">
+      <c r="H5" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>7.5242699999999996</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <v>99.758809999999997</v>
       </c>
-      <c r="G6" s="12">
+      <c r="H6" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>14.480402</v>
       </c>
-      <c r="F7" s="5">
+      <c r="G7" s="5">
         <v>101.726573</v>
       </c>
-      <c r="G7" s="12">
+      <c r="H7" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5">
-        <v>8.2214618999999995</v>
-      </c>
       <c r="F8" s="5">
-        <v>100.24672529999999</v>
-      </c>
-      <c r="G8" s="12">
+        <v>8.2057900000000004</v>
+      </c>
+      <c r="G8" s="5">
+        <v>100.25373999999999</v>
+      </c>
+      <c r="H8" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="5">
         <v>16.016102</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="13">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
-      <c r="G10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:7" ht="21" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:7" ht="21" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:7" ht="21" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:7" ht="21" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="21" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" ht="21" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" ht="21" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" ht="21" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" ht="21" x14ac:dyDescent="0.25"/>
     <row r="17" ht="21" x14ac:dyDescent="0.25"/>
     <row r="18" ht="21" x14ac:dyDescent="0.25"/>
     <row r="19" ht="21" x14ac:dyDescent="0.25"/>
@@ -1602,6 +1676,9 @@
     <row r="791" ht="21" x14ac:dyDescent="0.25"/>
     <row r="792" ht="21" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="F8:G8">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="55" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
